--- a/docs/deliverables/05_運用/運用手順書.xlsx
+++ b/docs/deliverables/05_運用/運用手順書.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="Rcd63fa533f984521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用体制" sheetId="2" r:id="R15399743e26b4584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="毎日" sheetId="3" r:id="Rca42e1d4144c4086"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="毎月" sheetId="4" r:id="Rab3ce4c60beb4f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四半期" sheetId="5" r:id="Rb07f05062a974797"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者管理" sheetId="6" r:id="R592d9692a18c4656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="バックアップ" sheetId="7" r:id="R47e78cd855d142f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="監視と障害対応" sheetId="8" r:id="Rd5b339c873d04513"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セキュリティ運用" sheetId="9" r:id="Raff503db82b844d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データ保持" sheetId="10" r:id="R0d05d898f5b94d21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R15bc21f437b64d3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用体制" sheetId="2" r:id="Re6e30a256c834b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="毎日" sheetId="3" r:id="R7cdba4a3aabc4957"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="毎月" sheetId="4" r:id="R2ff452c4b0504208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四半期" sheetId="5" r:id="R1321a06c3aca4fef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者管理" sheetId="6" r:id="R29fa81d44a784841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="バックアップ" sheetId="7" r:id="R433a71c3ea5e4c58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="監視と障害対応" sheetId="8" r:id="R4b20250b64b74cf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セキュリティ運用" sheetId="9" r:id="Re6a34059722e4256"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データ保持" sheetId="10" r:id="Ra2ea84eb99a24a1c"/>
   </x:sheets>
 </x:workbook>
 </file>
